--- a/fhir/core/ValueSet-sor-organization-type.xlsx
+++ b/fhir/core/ValueSet-sor-organization-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/core/ValueSet-sor-organization-type.xlsx
+++ b/fhir/core/ValueSet-sor-organization-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
